--- a/research/traditional_assets/database/data/sweden/sweden_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_brokerage_investment_banking.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.27</v>
+        <v>0.1456</v>
       </c>
       <c r="E2">
-        <v>0.435</v>
-      </c>
-      <c r="F2">
-        <v>0.46</v>
+        <v>0.452</v>
       </c>
       <c r="G2">
-        <v>0.006877528976064742</v>
+        <v>0.01423369210057798</v>
       </c>
       <c r="H2">
-        <v>-0.000602239215417324</v>
+        <v>-0.0006604211454843127</v>
       </c>
       <c r="I2">
-        <v>-0.000925862423702078</v>
+        <v>-0.0006650394751730141</v>
       </c>
       <c r="J2">
-        <v>-0.0008122083106599241</v>
+        <v>-0.0006330307392725272</v>
       </c>
       <c r="K2">
-        <v>444.282</v>
+        <v>141.532</v>
       </c>
       <c r="L2">
-        <v>0.4760926033879707</v>
+        <v>0.3268207187506494</v>
       </c>
       <c r="M2">
-        <v>62.907</v>
+        <v>80.92</v>
       </c>
       <c r="N2">
-        <v>0.005835198564830747</v>
+        <v>0.02144757906343098</v>
       </c>
       <c r="O2">
-        <v>0.1415925020595027</v>
+        <v>0.5717434926377074</v>
       </c>
       <c r="P2">
-        <v>59.247</v>
+        <v>75.83</v>
       </c>
       <c r="Q2">
-        <v>0.005495700150548068</v>
+        <v>0.0200984913541766</v>
       </c>
       <c r="R2">
-        <v>0.1333544910664848</v>
+        <v>0.5357798942995224</v>
       </c>
       <c r="S2">
-        <v>3.659999999999998</v>
+        <v>5.090000000000003</v>
       </c>
       <c r="T2">
-        <v>0.05818112451714434</v>
+        <v>0.06290163124073163</v>
       </c>
       <c r="U2">
-        <v>1191.45</v>
+        <v>832.6799999999999</v>
       </c>
       <c r="V2">
-        <v>0.1105178649445625</v>
+        <v>0.220699087179161</v>
       </c>
       <c r="W2">
-        <v>0.6259965012804087</v>
+        <v>-0.05010005973715651</v>
       </c>
       <c r="X2">
-        <v>0.03332461760518345</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y2">
-        <v>0.5926718836752253</v>
+        <v>-0.1158914709404119</v>
       </c>
       <c r="Z2">
-        <v>0.1519947618566742</v>
+        <v>0.06238852040967007</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03328077443950399</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC2">
-        <v>-0.03427321034804608</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD2">
-        <v>6934.33</v>
+        <v>6638.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6934.33</v>
+        <v>6638.5</v>
       </c>
       <c r="AG2">
-        <v>5742.88</v>
+        <v>5805.82</v>
       </c>
       <c r="AH2">
-        <v>0.3914396548901662</v>
+        <v>0.6376171550086347</v>
       </c>
       <c r="AI2">
-        <v>0.8553351054316252</v>
+        <v>0.9277076948661297</v>
       </c>
       <c r="AJ2">
-        <v>0.3475585363624755</v>
+        <v>0.6061152093072784</v>
       </c>
       <c r="AK2">
-        <v>0.8304119611897566</v>
+        <v>0.918187669714208</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.046</v>
+        <v>-0.042</v>
       </c>
       <c r="AN2">
-        <v>-12338.66548042705</v>
+        <v>-23211.53846153846</v>
       </c>
       <c r="AP2">
-        <v>-10218.64768683274</v>
+        <v>-20300.06993006993</v>
       </c>
       <c r="AQ2">
-        <v>18.78260869565218</v>
+        <v>6.857142857142856</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Avanza Bank Holding AB (publ) (OM:AZA)</t>
+          <t>Nordnet AB (publ) (OM:SAVE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.278</v>
+        <v>0.243</v>
       </c>
       <c r="E3">
-        <v>0.366</v>
+        <v>0.452</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.01773510307822649</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -740,85 +737,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>226.4</v>
+        <v>144.7</v>
       </c>
       <c r="L3">
-        <v>0.5495145631067961</v>
+        <v>0.4086416266591358</v>
       </c>
       <c r="M3">
-        <v>18.76</v>
+        <v>78.89</v>
       </c>
       <c r="N3">
-        <v>0.003283508943886302</v>
+        <v>0.02182416731216111</v>
       </c>
       <c r="O3">
-        <v>0.08286219081272084</v>
+        <v>0.5451969592259849</v>
       </c>
       <c r="P3">
-        <v>15.1</v>
+        <v>73.8</v>
       </c>
       <c r="Q3">
-        <v>0.002642909650995904</v>
+        <v>0.02041606727896426</v>
       </c>
       <c r="R3">
-        <v>0.06669611307420495</v>
+        <v>0.5100207325501037</v>
       </c>
       <c r="S3">
-        <v>3.659999999999998</v>
+        <v>5.090000000000003</v>
       </c>
       <c r="T3">
-        <v>0.195095948827292</v>
+        <v>0.06452021802509827</v>
       </c>
       <c r="U3">
-        <v>549.7</v>
+        <v>828.9</v>
       </c>
       <c r="V3">
-        <v>0.09621241292400323</v>
+        <v>0.229307292243001</v>
       </c>
       <c r="W3">
-        <v>0.7750770284149263</v>
+        <v>0.2367861233840615</v>
       </c>
       <c r="X3">
-        <v>0.03330213421731616</v>
+        <v>0.1051492986987216</v>
       </c>
       <c r="Y3">
-        <v>0.7417748941976101</v>
+        <v>0.1316368246853399</v>
       </c>
       <c r="Z3">
-        <v>2.715886618325642</v>
+        <v>0.05124234837850745</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03326347074914848</v>
+        <v>0.06534452126984863</v>
       </c>
       <c r="AC3">
-        <v>-0.03326347074914848</v>
+        <v>-0.06534452126984863</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>6638.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>6638.5</v>
       </c>
       <c r="AG3">
-        <v>-534.7</v>
+        <v>5809.6</v>
       </c>
       <c r="AH3">
-        <v>0.002618532225403254</v>
+        <v>0.6474500892395619</v>
       </c>
       <c r="AI3">
-        <v>0.02731245447924253</v>
+        <v>0.9310267450177412</v>
       </c>
       <c r="AJ3">
-        <v>-0.1032498503485431</v>
+        <v>0.6164424260430371</v>
       </c>
       <c r="AK3">
-        <v>1069.4</v>
+        <v>0.9219538515250579</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mangold Fondkommission AB (OM:MANG)</t>
+          <t>Safello Group AB (publ) (OM:SFL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,14 +840,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.254</v>
-      </c>
-      <c r="E4">
-        <v>0.8179999999999999</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.002677165354330709</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -862,85 +853,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>12.1</v>
+        <v>-2.32</v>
       </c>
       <c r="L4">
-        <v>0.3118556701030928</v>
+        <v>-0.03653543307086614</v>
       </c>
       <c r="M4">
-        <v>0.897</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.003367117117117117</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.07413223140495868</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>0.897</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.003367117117117117</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.07413223140495868</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.2506426735218509</v>
       </c>
       <c r="W4">
-        <v>0.9097744360902255</v>
+        <v>-0.3213296398891967</v>
       </c>
       <c r="X4">
-        <v>0.03334710099305073</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y4">
-        <v>0.8764273350971747</v>
+        <v>-0.387121051092452</v>
       </c>
       <c r="Z4">
-        <v>2.621621621621621</v>
+        <v>40.47163798597833</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0332972794093698</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC4">
-        <v>-0.0332972794093698</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD4">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.53</v>
+        <v>-1.95</v>
       </c>
       <c r="AH4">
-        <v>0.005710446758481694</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.05810862134447398</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.005710446758481694</v>
+        <v>-0.3344768439108062</v>
       </c>
       <c r="AK4">
-        <v>0.05810862134447398</v>
+        <v>-1.382978723404255</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nordnet AB (publ) (OM:SAVE)</t>
+          <t>Mangold Fondkommission AB (OM:MANG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,16 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.27</v>
-      </c>
-      <c r="E5">
-        <v>0.435</v>
-      </c>
-      <c r="F5">
-        <v>0.46</v>
+        <v>0.0482</v>
       </c>
       <c r="G5">
-        <v>0.01445733222866612</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -987,28 +969,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>206.6</v>
+        <v>-0.602</v>
       </c>
       <c r="L5">
-        <v>0.427920463960232</v>
+        <v>-0.03909090909090909</v>
       </c>
       <c r="M5">
-        <v>43.25</v>
+        <v>2.03</v>
       </c>
       <c r="N5">
-        <v>0.00901417257190496</v>
+        <v>0.01388508891928865</v>
       </c>
       <c r="O5">
-        <v>0.2093417231364957</v>
+        <v>-3.372093023255814</v>
       </c>
       <c r="P5">
-        <v>43.25</v>
+        <v>2.03</v>
       </c>
       <c r="Q5">
-        <v>0.00901417257190496</v>
+        <v>0.01388508891928865</v>
       </c>
       <c r="R5">
-        <v>0.2093417231364957</v>
+        <v>-3.372093023255814</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,55 +999,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>639.8</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.1333472280116715</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.476915974145891</v>
+        <v>-0.0242741935483871</v>
       </c>
       <c r="X5">
-        <v>0.05405866004271612</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y5">
-        <v>0.422857314103175</v>
+        <v>-0.09006560475164245</v>
       </c>
       <c r="Z5">
-        <v>0.08087237642171562</v>
+        <v>0.5848841625522218</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03524914128672237</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC5">
-        <v>-0.03524914128672237</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD5">
-        <v>6917.8</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>6917.8</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>6278</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.5904675737038871</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.9188327644144563</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.5668111231491513</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.9112946538735103</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1091,22 +1073,22 @@
         </is>
       </c>
       <c r="G6">
-        <v>1.350961538461539</v>
+        <v>-5.017543859649122</v>
       </c>
       <c r="H6">
-        <v>1.350961538461539</v>
+        <v>-5.017543859649122</v>
       </c>
       <c r="I6">
-        <v>2.076923076923077</v>
+        <v>-5.052631578947368</v>
       </c>
       <c r="J6">
-        <v>2.076923076923077</v>
+        <v>-5.052631578947368</v>
       </c>
       <c r="K6">
-        <v>-0.8179999999999999</v>
+        <v>-0.246</v>
       </c>
       <c r="L6">
-        <v>1.966346153846154</v>
+        <v>-4.315789473684211</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1130,31 +1112,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>0.693950177935943</v>
+        <v>0.4420289855072465</v>
       </c>
       <c r="W6">
-        <v>-0.2471299093655589</v>
+        <v>-0.07592592592592592</v>
       </c>
       <c r="X6">
-        <v>0.03326426946963817</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y6">
-        <v>-0.2803941788351971</v>
+        <v>-0.1417173371291813</v>
       </c>
       <c r="Z6">
-        <v>-0.1308176100628931</v>
+        <v>0.01842275371687136</v>
       </c>
       <c r="AA6">
-        <v>-0.2716981132075472</v>
+        <v>-0.09308338720103425</v>
       </c>
       <c r="AB6">
-        <v>0.03326426946963817</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC6">
-        <v>-0.3049623826771853</v>
+        <v>-0.1588747984042896</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1166,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-1.95</v>
+        <v>-1.83</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1175,25 +1157,25 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-2.267441860465116</v>
+        <v>-0.7922077922077924</v>
       </c>
       <c r="AK6">
-        <v>-2.532467532467531</v>
+        <v>-2.541666666666668</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.046</v>
+        <v>-0.042</v>
       </c>
       <c r="AN6">
         <v>-0</v>
       </c>
       <c r="AP6">
-        <v>3.469750889679715</v>
+        <v>6.398601398601399</v>
       </c>
       <c r="AQ6">
-        <v>18.78260869565218</v>
+        <v>6.857142857142856</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_brokerage_investment_banking.xlsx
@@ -588,118 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1456</v>
+        <v>0.146555</v>
       </c>
       <c r="E2">
-        <v>0.452</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="G2">
-        <v>0.01423369210057798</v>
+        <v>0.01421094057457694</v>
       </c>
       <c r="H2">
-        <v>-0.0006604211454843127</v>
+        <v>-0.000295159386068477</v>
       </c>
       <c r="I2">
-        <v>-0.0006650394751730141</v>
+        <v>-0.001493506493506494</v>
       </c>
       <c r="J2">
-        <v>-0.0006330307392725272</v>
+        <v>-0.001426133368476542</v>
       </c>
       <c r="K2">
-        <v>141.532</v>
+        <v>218.371</v>
       </c>
       <c r="L2">
-        <v>0.3268207187506494</v>
+        <v>0.4296950019677292</v>
       </c>
       <c r="M2">
-        <v>80.92</v>
+        <v>127.4</v>
       </c>
       <c r="N2">
-        <v>0.02144757906343098</v>
+        <v>0.02901204204696581</v>
       </c>
       <c r="O2">
-        <v>0.5717434926377074</v>
+        <v>0.583410800884733</v>
       </c>
       <c r="P2">
-        <v>75.83</v>
+        <v>127.4</v>
       </c>
       <c r="Q2">
-        <v>0.0200984913541766</v>
+        <v>0.02901204204696581</v>
       </c>
       <c r="R2">
-        <v>0.5357798942995224</v>
+        <v>0.583410800884733</v>
       </c>
       <c r="S2">
-        <v>5.090000000000003</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.06290163124073163</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>832.6799999999999</v>
+        <v>121.745</v>
       </c>
       <c r="V2">
-        <v>0.220699087179161</v>
+        <v>0.02772426262957498</v>
       </c>
       <c r="W2">
-        <v>-0.05010005973715651</v>
+        <v>-0.1404336734693877</v>
       </c>
       <c r="X2">
-        <v>0.06579141120325535</v>
+        <v>0.05719065640181126</v>
       </c>
       <c r="Y2">
-        <v>-0.1158914709404119</v>
+        <v>-0.197624329871199</v>
       </c>
       <c r="Z2">
-        <v>0.06238852040967007</v>
+        <v>0.08034895668887672</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06579141120325535</v>
+        <v>0.05652881523203043</v>
       </c>
       <c r="AC2">
-        <v>-0.06579141120325535</v>
+        <v>-0.05652881523203043</v>
       </c>
       <c r="AD2">
-        <v>6638.5</v>
+        <v>5532.95</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6638.5</v>
+        <v>5532.95</v>
       </c>
       <c r="AG2">
-        <v>5805.82</v>
+        <v>5411.205</v>
       </c>
       <c r="AH2">
-        <v>0.6376171550086347</v>
+        <v>0.5575193239173215</v>
       </c>
       <c r="AI2">
-        <v>0.9277076948661297</v>
+        <v>0.8916677544692571</v>
       </c>
       <c r="AJ2">
-        <v>0.6061152093072784</v>
+        <v>0.5520237980471278</v>
       </c>
       <c r="AK2">
-        <v>0.918187669714208</v>
+        <v>0.8894997472640823</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.042</v>
+        <v>-0.012</v>
       </c>
       <c r="AN2">
-        <v>-23211.53846153846</v>
+        <v>-7280.197368421052</v>
       </c>
       <c r="AP2">
-        <v>-20300.06993006993</v>
+        <v>-7120.006578947368</v>
       </c>
       <c r="AQ2">
-        <v>6.857142857142856</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.243</v>
+        <v>0.285</v>
       </c>
       <c r="E3">
-        <v>0.452</v>
+        <v>0.9359999999999999</v>
       </c>
       <c r="G3">
-        <v>0.01773510307822649</v>
+        <v>0.01613192730536235</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -737,85 +737,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>144.7</v>
+        <v>222.1</v>
       </c>
       <c r="L3">
-        <v>0.4086416266591358</v>
+        <v>0.4983172537581333</v>
       </c>
       <c r="M3">
-        <v>78.89</v>
+        <v>127.4</v>
       </c>
       <c r="N3">
-        <v>0.02182416731216111</v>
+        <v>0.02991733984595154</v>
       </c>
       <c r="O3">
-        <v>0.5451969592259849</v>
+        <v>0.5736154885186853</v>
       </c>
       <c r="P3">
-        <v>73.8</v>
+        <v>127.4</v>
       </c>
       <c r="Q3">
-        <v>0.02041606727896426</v>
+        <v>0.02991733984595154</v>
       </c>
       <c r="R3">
-        <v>0.5100207325501037</v>
+        <v>0.5736154885186853</v>
       </c>
       <c r="S3">
-        <v>5.090000000000003</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.06452021802509827</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>828.9</v>
+        <v>119.9</v>
       </c>
       <c r="V3">
-        <v>0.229307292243001</v>
+        <v>0.02815611497275973</v>
       </c>
       <c r="W3">
-        <v>0.2367861233840615</v>
+        <v>0.4516063440422936</v>
       </c>
       <c r="X3">
-        <v>0.1051492986987216</v>
+        <v>0.07494717910815303</v>
       </c>
       <c r="Y3">
-        <v>0.1316368246853399</v>
+        <v>0.3766591649341406</v>
       </c>
       <c r="Z3">
-        <v>0.05124234837850745</v>
+        <v>0.07073031389849874</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06534452126984863</v>
+        <v>0.0554284219563824</v>
       </c>
       <c r="AC3">
-        <v>-0.06534452126984863</v>
+        <v>-0.0554284219563824</v>
       </c>
       <c r="AD3">
-        <v>6638.5</v>
+        <v>5523</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6638.5</v>
+        <v>5523</v>
       </c>
       <c r="AG3">
-        <v>5809.6</v>
+        <v>5403.1</v>
       </c>
       <c r="AH3">
-        <v>0.6474500892395619</v>
+        <v>0.5646430981250128</v>
       </c>
       <c r="AI3">
-        <v>0.9310267450177412</v>
+        <v>0.8948476992871031</v>
       </c>
       <c r="AJ3">
-        <v>0.6164424260430371</v>
+        <v>0.5592402835998551</v>
       </c>
       <c r="AK3">
-        <v>0.9219538515250579</v>
+        <v>0.8927644949686886</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Safello Group AB (publ) (OM:SFL)</t>
+          <t>Mangold Fondkommission AB (OM:MANG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,8 +840,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.008110000000000001</v>
+      </c>
       <c r="G4">
-        <v>0.002677165354330709</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -853,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-2.32</v>
+        <v>-2.46</v>
       </c>
       <c r="L4">
-        <v>-0.03653543307086614</v>
+        <v>-0.1835820895522388</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.2506426735218509</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>-0.3213296398891967</v>
+        <v>-0.1255102040816326</v>
       </c>
       <c r="X4">
-        <v>0.06579141120325535</v>
+        <v>0.05777298717564693</v>
       </c>
       <c r="Y4">
-        <v>-0.387121051092452</v>
+        <v>-0.1832831912572795</v>
       </c>
       <c r="Z4">
-        <v>40.47163798597833</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06579141120325535</v>
+        <v>0.05644930483608526</v>
       </c>
       <c r="AC4">
-        <v>-0.06579141120325535</v>
+        <v>-0.05644930483608526</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AG4">
-        <v>-1.95</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.07609942638623327</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.3585585585585586</v>
       </c>
       <c r="AJ4">
-        <v>-0.3344768439108062</v>
+        <v>0.07609942638623327</v>
       </c>
       <c r="AK4">
-        <v>-1.382978723404255</v>
+        <v>0.3585585585585586</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mangold Fondkommission AB (OM:MANG)</t>
+          <t>Safello Group AB (publ) (OM:SFL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -953,11 +956,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0482</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.003706720977596741</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -969,61 +969,58 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.602</v>
+        <v>-0.522</v>
       </c>
       <c r="L5">
-        <v>-0.03909090909090909</v>
+        <v>-0.01063136456211813</v>
       </c>
       <c r="M5">
-        <v>2.03</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.01388508891928865</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-3.372093023255814</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>2.03</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.01388508891928865</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>-3.372093023255814</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>0.1758360302049622</v>
       </c>
       <c r="W5">
-        <v>-0.0242741935483871</v>
+        <v>-0.1553571428571429</v>
       </c>
       <c r="X5">
-        <v>0.06579141120325535</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="Y5">
-        <v>-0.09006560475164245</v>
+        <v>-0.2119654684851185</v>
       </c>
       <c r="Z5">
-        <v>0.5848841625522218</v>
+        <v>54.73801560758083</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06579141120325535</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="AC5">
-        <v>-0.06579141120325535</v>
+        <v>-0.0566083256279756</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1035,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>-1.63</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1044,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>-0.2133507853403141</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>-1.244274809160305</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1072,23 +1069,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G6">
-        <v>-5.017543859649122</v>
-      </c>
-      <c r="H6">
-        <v>-5.017543859649122</v>
-      </c>
-      <c r="I6">
-        <v>-5.052631578947368</v>
-      </c>
-      <c r="J6">
-        <v>-5.052631578947368</v>
-      </c>
       <c r="K6">
-        <v>-0.246</v>
-      </c>
-      <c r="L6">
-        <v>-4.315789473684211</v>
+        <v>-0.747</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,31 +1094,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.83</v>
+        <v>0.215</v>
       </c>
       <c r="V6">
-        <v>0.4420289855072465</v>
+        <v>0.07651245551601424</v>
       </c>
       <c r="W6">
-        <v>-0.07592592592592592</v>
+        <v>-0.2146551724137931</v>
       </c>
       <c r="X6">
-        <v>0.06579141120325535</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="Y6">
-        <v>-0.1417173371291813</v>
+        <v>-0.2712634980417687</v>
       </c>
       <c r="Z6">
-        <v>0.01842275371687136</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.09308338720103425</v>
+        <v>-0.2518248175182482</v>
       </c>
       <c r="AB6">
-        <v>0.06579141120325535</v>
+        <v>0.0566083256279756</v>
       </c>
       <c r="AC6">
-        <v>-0.1588747984042896</v>
+        <v>-0.3084331431462238</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1148,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-1.83</v>
+        <v>-0.215</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1157,25 +1139,25 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.7922077922077924</v>
+        <v>-0.08285163776493255</v>
       </c>
       <c r="AK6">
-        <v>-2.541666666666668</v>
+        <v>-0.09492273730684327</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.042</v>
+        <v>-0.012</v>
       </c>
       <c r="AN6">
         <v>-0</v>
       </c>
       <c r="AP6">
-        <v>6.398601398601399</v>
+        <v>0.2828947368421053</v>
       </c>
       <c r="AQ6">
-        <v>6.857142857142856</v>
+        <v>63.25</v>
       </c>
     </row>
   </sheetData>
